--- a/summary_2026-05-14.xlsx
+++ b/summary_2026-05-14.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Party Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Top by Spend" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Top by Impressions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Active Ads" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Removed Ads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MT — Party Overview" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MT — Active Ads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CY — Party Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CY — Top by Spend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CY — Top by Impressions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CY — Active Ads" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CY — Removed Ads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MT — Party Overview" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MT — Active Ads" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,10 +611,10 @@
         <v>312</v>
       </c>
       <c r="F5" t="n">
-        <v>808897</v>
+        <v>749900</v>
       </c>
       <c r="G5" t="n">
-        <v>10197</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="6">
@@ -661,10 +661,10 @@
         <v>107</v>
       </c>
       <c r="F7" t="n">
-        <v>11998</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -861,10 +861,10 @@
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>479998</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -936,10 +936,10 @@
         <v>1537</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1668856</v>
+        <v>1117863</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14956</v>
+        <v>13563</v>
       </c>
     </row>
   </sheetData>
@@ -1066,13 +1066,13 @@
         <v>99</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>29999</v>
+        <v>24999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9009</v>
+        <v>8811</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>670909</v>
+        <v>620911</v>
       </c>
     </row>
     <row r="5">
@@ -1116,141 +1116,141 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Ερωτοκρίτου Χριστιάνα</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Χριστιάνα Ερωτοκρίτου</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>699</v>
+        <v>199</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>399999</v>
+        <v>89999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>898</v>
+        <v>792</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>479998</v>
+        <v>90992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ερωτοκρίτου Χριστιάνα</t>
+          <t>Φελλάς Μιχάλης</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Χριστιάνα Ερωτοκρίτου</t>
+          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>199</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>89999</v>
+        <v>199999</v>
       </c>
       <c r="I7" t="n">
-        <v>792</v>
+        <v>693</v>
       </c>
       <c r="J7" t="n">
-        <v>90992</v>
+        <v>114993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
+          <t>ΑΚΕΛ - AKEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>499</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>199999</v>
+        <v>24999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>693</v>
+        <v>594</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>114993</v>
+        <v>49994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>Πετρίδης Χαράλαμπος</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ - AKEL</t>
+          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
         <v>99</v>
@@ -1259,178 +1259,178 @@
         <v>24999</v>
       </c>
       <c r="I9" t="n">
-        <v>594</v>
+        <v>297</v>
       </c>
       <c r="J9" t="n">
-        <v>49994</v>
+        <v>35997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Πετρίδης Χαράλαμπος</t>
+          <t>Θεμιστοκλέους Ανδρέας</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
+          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>24999</v>
+        <v>5999</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>297</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>35997</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Θεμιστοκλέους Ανδρέας</t>
+          <t>Σαββίδης Χρύσανθος</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
+          <t>Χρύσανθος Σαββίδης</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H11" t="n">
-        <v>5999</v>
+        <v>149999</v>
       </c>
       <c r="I11" t="n">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="J11" t="n">
-        <v>8997</v>
+        <v>33998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Σαββίδης Χρύσανθος</t>
+          <t>Τσιρίδου Φωτεινή</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Χρύσανθος Σαββίδης</t>
+          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>149999</v>
+        <v>39999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Παλιος Νίκος</t>
+          <t>Σενέκης Χρίστος</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ΑΜΔΗ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Νίκος Παλιός</t>
+          <t>Χρίστος Σενέκης</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>14999</v>
+        <v>3999</v>
       </c>
       <c r="I13" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="J13" t="n">
-        <v>11998</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Τσιρίδου Φωτεινή</t>
+          <t>Νικολαΐδης Ζήνωνας</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΟΙΚΟΛΟΓΟΙ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
+          <t>Zenonas Nicolaides</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1440,159 +1440,159 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>39999</v>
+        <v>14999</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>99</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>999</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Σενέκης Χρίστος</t>
+          <t>Μούντουκκος Κωνσταντίνος</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Χρίστος Σενέκης</t>
+          <t>Constantinos Mountouckos</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>99</v>
       </c>
       <c r="H15" t="n">
-        <v>3999</v>
+        <v>14999</v>
       </c>
       <c r="I15" t="n">
         <v>99</v>
       </c>
       <c r="J15" t="n">
-        <v>3999</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Παπαδοπουλος Γεώργιος</t>
+          <t>Χειμωνίδης Ανδρέας</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Γεώργιος Παπαδόπουλος-Georgios Papadopoulos</t>
+          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8999</v>
+        <v>4999</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Νικολαΐδης Ζήνωνας</t>
+          <t>Χατζηπαυλου Αυγή</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ΟΙΚΟΛΟΓΟΙ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zenonas Nicolaides</t>
+          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>14999</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>14999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Μούντουκκος Κωνσταντίνος</t>
+          <t>Χαπεσιάν Άρι</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Constantinos Mountouckos</t>
+          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>99</v>
@@ -1601,42 +1601,42 @@
         <v>14999</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Χειμωνίδης Ανδρέας</t>
+          <t>Χαμπούλλας Ευγένιος</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>4999</v>
+        <v>8999</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1648,27 +1648,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Χατζηπαυλου Αυγή</t>
+          <t>Φράγκου Αντωνία</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
+          <t>antoniafrangou2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1686,33 +1686,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Χαπεσιάν Άρι</t>
+          <t>Φλουρεντζου Μάριος</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
+          <t>Marios Flourentzou</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>14999</v>
+        <v>5999</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Φλουρέντζου Μάριος</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1734,23 +1734,23 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>62</v>
-      </c>
       <c r="F22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
@@ -1762,33 +1762,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Φράγκου Αντωνία</t>
+          <t>Φελλας Μιχάλης</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>antoniafrangou2026</t>
+          <t>Michalis Fellas</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>19999</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1800,33 +1800,33 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Φλουρεντζου Μάριος</t>
+          <t>Τσολάκη Ευανθία</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marios Flourentzou</t>
+          <t>Ευανθία - Εύη - Τσολάκη</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5999</v>
+        <v>249999</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -1838,33 +1838,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Φλουρέντζου Μάριος</t>
+          <t>Τσατσου Θεόδωρος</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
+          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2999</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1876,33 +1876,33 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Φελλας Μιχάλης</t>
+          <t>Τσαγγάρης Ανδρέας</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Michalis Fellas</t>
+          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="F26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>19999</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
@@ -1914,33 +1914,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Τσολάκη Ευανθία</t>
+          <t>Σωτηρίου Ανδρέας</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ευανθία - Εύη - Τσολάκη</t>
+          <t>ΔΕΚ - Δημοκρατικό Εθνικό Κίνημα</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="H27" t="n">
-        <v>249999</v>
+        <v>5999</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1952,24 +1952,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Τσατσου Θεόδωρος</t>
+          <t>Στυλιανού Στέλιος</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΕΝΕΡΓΟΙ ΠΟΛΙΤΕΣ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
+          <t>Stelios Stylianou</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
@@ -1978,7 +1978,7 @@
         <v>99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2999</v>
+        <v>8999</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
@@ -1990,24 +1990,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Τσαγγάρης Ανδρέας</t>
+          <t>Στυλιανού Μάριος</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>olathrepivatis</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2028,33 +2028,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Σωτηρίου Ανδρέας</t>
+          <t>Στυλιανού Μάριος</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ - Δημοκρατικό Εθνικό Κίνημα</t>
+          <t>Μάριος Στυλιανού</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5999</v>
+        <v>4999</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>0</v>
@@ -2066,33 +2066,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Στυλιανού Στέλιος</t>
+          <t>Στυλιανού Μάριος</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ΕΝΕΡΓΟΙ ΠΟΛΙΤΕΣ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stelios Stylianou</t>
+          <t>Marios Stylianou</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2104,33 +2104,33 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Στυλιανού Γιώργος</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>olathrepivatis</t>
+          <t>Δημοκρατική Αλλαγή</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>3999</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
@@ -2142,33 +2142,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Στυλιανού Γιάννος</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Μάριος Στυλιανού</t>
+          <t>Στυλιανού Γιάννος</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4999</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2301,191 +2301,191 @@
         <v>99</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>29999</v>
+        <v>24999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9009</v>
+        <v>8811</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>670909</v>
+        <v>620911</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Παπαβασιλείου Σταμάτης</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΟΙΚΟΛΟΓΟΙ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Σταμάτης Στάμος Παπαβασιλείου</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>699</v>
+        <v>99</v>
       </c>
       <c r="H5" t="n">
-        <v>399999</v>
+        <v>19999</v>
       </c>
       <c r="I5" t="n">
-        <v>898</v>
+        <v>1485</v>
       </c>
       <c r="J5" t="n">
-        <v>479998</v>
+        <v>126985</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Παπαβασιλείου Σταμάτης</t>
+          <t>Φελλάς Μιχάλης</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ΟΙΚΟΛΟΓΟΙ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Σταμάτης Στάμος Παπαβασιλείου</t>
+          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>99</v>
+        <v>499</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19999</v>
+        <v>199999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1485</v>
+        <v>693</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>126985</v>
+        <v>114993</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης</t>
+          <t>Ερωτοκρίτου Χριστιάνα</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
+          <t>Χριστιάνα Ερωτοκρίτου</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
-        <v>199999</v>
+        <v>89999</v>
       </c>
       <c r="I7" t="n">
-        <v>693</v>
+        <v>792</v>
       </c>
       <c r="J7" t="n">
-        <v>114993</v>
+        <v>90992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Ερωτοκρίτου Χριστιάνα</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Χριστιάνα Ερωτοκρίτου</t>
+          <t>ΑΚΕΛ - AKEL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>89999</v>
+        <v>24999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>792</v>
+        <v>594</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>90992</v>
+        <v>49994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>Πετρίδης Χαράλαμπος</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ - AKEL</t>
+          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
         <v>99</v>
@@ -2494,112 +2494,112 @@
         <v>24999</v>
       </c>
       <c r="I9" t="n">
-        <v>594</v>
+        <v>297</v>
       </c>
       <c r="J9" t="n">
-        <v>49994</v>
+        <v>35997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Πετρίδης Χαράλαμπος</t>
+          <t>Σαββίδης Χρύσανθος</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
+          <t>Χρύσανθος Σαββίδης</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>24999</v>
+        <v>149999</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>35997</v>
+        <v>33998</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Σαββίδης Χρύσανθος</t>
+          <t>Νικολαΐδης Ζήνωνας</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΟΙΚΟΛΟΓΟΙ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Χρύσανθος Σαββίδης</t>
+          <t>Zenonas Nicolaides</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="H11" t="n">
-        <v>149999</v>
+        <v>14999</v>
       </c>
       <c r="I11" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="J11" t="n">
-        <v>33998</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Νικολαΐδης Ζήνωνας</t>
+          <t>Μούντουκκος Κωνσταντίνος</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ΟΙΚΟΛΟΓΟΙ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Zenonas Nicolaides</t>
+          <t>Constantinos Mountouckos</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>99</v>
@@ -2617,207 +2617,207 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Μούντουκκος Κωνσταντίνος</t>
+          <t>Θεμιστοκλέους Ανδρέας</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Constantinos Mountouckos</t>
+          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>14999</v>
+        <v>5999</v>
       </c>
       <c r="I13" t="n">
-        <v>99</v>
+        <v>297</v>
       </c>
       <c r="J13" t="n">
-        <v>14999</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Παλιος Νίκος</t>
+          <t>Σενέκης Χρίστος</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ΑΜΔΗ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Νίκος Παλιός</t>
+          <t>Χρίστος Σενέκης</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>14999</v>
+        <v>3999</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>11998</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Παπαδοπουλος Γεώργιος</t>
+          <t>Τσιρίδου Φωτεινή</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Γεώργιος Παπαδόπουλος-Georgios Papadopoulos</t>
+          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>99</v>
       </c>
       <c r="H15" t="n">
-        <v>8999</v>
+        <v>39999</v>
       </c>
       <c r="I15" t="n">
         <v>99</v>
       </c>
       <c r="J15" t="n">
-        <v>8999</v>
+        <v>999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Θεμιστοκλέους Ανδρέας</t>
+          <t>Χειμωνίδης Ανδρέας</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
+          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5999</v>
+        <v>4999</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Σενέκης Χρίστος</t>
+          <t>Χατζηπαυλου Αυγή</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Χρίστος Σενέκης</t>
+          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3999</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Τσιρίδου Φωτεινή</t>
+          <t>Χαπεσιάν Άρι</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
+          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -2827,51 +2827,51 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>39999</v>
+        <v>14999</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Χειμωνίδης Ανδρέας</t>
+          <t>Χαμπούλλας Ευγένιος</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>4999</v>
+        <v>8999</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2883,27 +2883,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Χατζηπαυλου Αυγή</t>
+          <t>Φράγκου Αντωνία</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
+          <t>antoniafrangou2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2921,33 +2921,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Χαπεσιάν Άρι</t>
+          <t>Φλουρεντζου Μάριος</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
+          <t>Marios Flourentzou</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>14999</v>
+        <v>5999</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2959,7 +2959,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Φλουρέντζου Μάριος</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2969,23 +2969,23 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>62</v>
-      </c>
       <c r="F22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
@@ -2997,33 +2997,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Φράγκου Αντωνία</t>
+          <t>Φελλας Μιχάλης</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>antoniafrangou2026</t>
+          <t>Michalis Fellas</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>19999</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3035,33 +3035,33 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Φλουρεντζου Μάριος</t>
+          <t>Τσολάκη Ευανθία</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marios Flourentzou</t>
+          <t>Ευανθία - Εύη - Τσολάκη</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5999</v>
+        <v>249999</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -3073,33 +3073,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Φλουρέντζου Μάριος</t>
+          <t>Τσατσου Θεόδωρος</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
+          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2999</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3111,33 +3111,33 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Φελλας Μιχάλης</t>
+          <t>Τσαγγάρης Ανδρέας</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Michalis Fellas</t>
+          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="F26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>19999</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
@@ -3149,33 +3149,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Τσολάκη Ευανθία</t>
+          <t>Σωτηρίου Ανδρέας</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ευανθία - Εύη - Τσολάκη</t>
+          <t>ΔΕΚ - Δημοκρατικό Εθνικό Κίνημα</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="H27" t="n">
-        <v>249999</v>
+        <v>5999</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3187,24 +3187,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Τσατσου Θεόδωρος</t>
+          <t>Στυλιανού Στέλιος</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΕΝΕΡΓΟΙ ΠΟΛΙΤΕΣ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
+          <t>Stelios Stylianou</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2999</v>
+        <v>8999</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
@@ -3225,24 +3225,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Τσαγγάρης Ανδρέας</t>
+          <t>Στυλιανού Μάριος</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>olathrepivatis</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -3263,33 +3263,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Σωτηρίου Ανδρέας</t>
+          <t>Στυλιανού Μάριος</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ - Δημοκρατικό Εθνικό Κίνημα</t>
+          <t>Μάριος Στυλιανού</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5999</v>
+        <v>4999</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>0</v>
@@ -3301,33 +3301,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Στυλιανού Στέλιος</t>
+          <t>Στυλιανού Μάριος</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ΕΝΕΡΓΟΙ ΠΟΛΙΤΕΣ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stelios Stylianou</t>
+          <t>Marios Stylianou</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3339,33 +3339,33 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Στυλιανού Γιώργος</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>olathrepivatis</t>
+          <t>Δημοκρατική Αλλαγή</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>3999</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
@@ -3377,33 +3377,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Στυλιανού Γιάννος</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Μάριος Στυλιανού</t>
+          <t>Στυλιανού Γιάννος</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4999</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3433,8 +3433,8 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3536,16 +3536,8 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,000–19,999</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0–99</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3622,16 +3614,8 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,000–29,999</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0–99</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3786,16 +3770,8 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,000–3,999</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0–99</t>
-        </is>
-      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3833,16 +3809,8 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>7,000–7,999</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0–99</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4348,16 +4316,8 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>8,000–8,999</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0–99</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4434,16 +4394,8 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>350,000–399,999</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>600–699</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4637,16 +4589,8 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>70,000–79,999</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100–199</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">

--- a/summary_2026-05-14.xlsx
+++ b/summary_2026-05-14.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CY — Party Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CY — Top by Spend" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CY — Top by Impressions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CY — Active Ads" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CY — Removed Ads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MT — Party Overview" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MT — Active Ads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Party Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Top by Spend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Top by Impressions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Active Ads" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CY — Removed Ads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MT — Party Overview" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MT — Active Ads" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>261</v>
@@ -583,7 +583,7 @@
         <v>360</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>166988</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>188</v>
@@ -608,13 +608,13 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F5" t="n">
-        <v>749900</v>
+        <v>808897</v>
       </c>
       <c r="G5" t="n">
-        <v>9900</v>
+        <v>10197</v>
       </c>
     </row>
     <row r="6">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>74</v>
@@ -633,7 +633,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>90</v>
@@ -658,13 +658,13 @@
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>11998</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         <v>41</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>4</v>
@@ -733,7 +733,7 @@
         <v>54</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
         <v>29</v>
@@ -758,7 +758,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>49994</v>
@@ -770,51 +770,51 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>8997</v>
-      </c>
       <c r="G12" s="2" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="D13" t="n">
-        <v>28</v>
-      </c>
       <c r="E13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>8997</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>7</v>
@@ -833,7 +833,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>479998</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>898</v>
       </c>
     </row>
     <row r="16">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>764</v>
@@ -933,13 +933,13 @@
         <v>744</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1537</v>
+        <v>1602</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1117863</v>
+        <v>1668856</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13563</v>
+        <v>14956</v>
       </c>
     </row>
   </sheetData>
@@ -957,7 +957,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="53" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1066,13 +1066,13 @@
         <v>99</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24999</v>
+        <v>29999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>8811</v>
+        <v>9009</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>620911</v>
+        <v>670909</v>
       </c>
     </row>
     <row r="5">
@@ -1116,141 +1116,141 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ερωτοκρίτου Χριστιάνα</t>
+          <t>Κληρίδης Αλέξανδρος</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΑ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Χριστιάνα Ερωτοκρίτου</t>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>17</v>
-      </c>
       <c r="G6" s="2" t="n">
-        <v>199</v>
+        <v>699</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>89999</v>
+        <v>399999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>792</v>
+        <v>898</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>90992</v>
+        <v>479998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης</t>
+          <t>Ερωτοκρίτου Χριστιάνα</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
+          <t>Χριστιάνα Ερωτοκρίτου</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
-        <v>199999</v>
+        <v>89999</v>
       </c>
       <c r="I7" t="n">
-        <v>693</v>
+        <v>792</v>
       </c>
       <c r="J7" t="n">
-        <v>114993</v>
+        <v>90992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>Φελλάς Μιχάλης</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ - AKEL</t>
+          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>99</v>
+        <v>499</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24999</v>
+        <v>199999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>594</v>
+        <v>693</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49994</v>
+        <v>114993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Πετρίδης Χαράλαμπος</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
+          <t>ΑΚΕΛ - AKEL</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>99</v>
@@ -1259,178 +1259,178 @@
         <v>24999</v>
       </c>
       <c r="I9" t="n">
-        <v>297</v>
+        <v>594</v>
       </c>
       <c r="J9" t="n">
-        <v>35997</v>
+        <v>49994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Θεμιστοκλέους Ανδρέας</t>
+          <t>Πετρίδης Χαράλαμπος</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
+          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5999</v>
+        <v>24999</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>297</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8997</v>
+        <v>35997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Σαββίδης Χρύσανθος</t>
+          <t>Θεμιστοκλέους Ανδρέας</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Χρύσανθος Σαββίδης</t>
+          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="H11" t="n">
-        <v>149999</v>
+        <v>5999</v>
       </c>
       <c r="I11" t="n">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="J11" t="n">
-        <v>33998</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Τσιρίδου Φωτεινή</t>
+          <t>Σαββίδης Χρύσανθος</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
+          <t>Χρύσανθος Σαββίδης</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>39999</v>
+        <v>149999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>999</v>
+        <v>33998</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Σενέκης Χρίστος</t>
+          <t>Παλιος Νίκος</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Χρίστος Σενέκης</t>
+          <t>Νίκος Παλιός</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>3999</v>
+        <v>14999</v>
       </c>
       <c r="I13" t="n">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="J13" t="n">
-        <v>3999</v>
+        <v>11998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Νικολαΐδης Ζήνωνας</t>
+          <t>Τσιρίδου Φωτεινή</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ΟΙΚΟΛΟΓΟΙ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Zenonas Nicolaides</t>
+          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1440,159 +1440,159 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>14999</v>
+        <v>39999</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>99</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14999</v>
+        <v>999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Μούντουκκος Κωνσταντίνος</t>
+          <t>Σενέκης Χρίστος</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Constantinos Mountouckos</t>
+          <t>Χρίστος Σενέκης</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>99</v>
       </c>
       <c r="H15" t="n">
-        <v>14999</v>
+        <v>3999</v>
       </c>
       <c r="I15" t="n">
         <v>99</v>
       </c>
       <c r="J15" t="n">
-        <v>14999</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Χειμωνίδης Ανδρέας</t>
+          <t>Παπαδοπουλος Γεώργιος</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
+          <t>Γεώργιος Παπαδόπουλος-Georgios Papadopoulos</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4999</v>
+        <v>8999</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Χατζηπαυλου Αυγή</t>
+          <t>Νικολαΐδης Ζήνωνας</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΟΙΚΟΛΟΓΟΙ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
+          <t>Zenonas Nicolaides</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>14999</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Χαπεσιάν Άρι</t>
+          <t>Μούντουκκος Κωνσταντίνος</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
+          <t>Constantinos Mountouckos</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>99</v>
@@ -1601,42 +1601,42 @@
         <v>14999</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Χρίστου Έλεν</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>Tothemaonline.com</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1648,17 +1648,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Φράγκου Αντωνία</t>
+          <t>Χειμωνίδης Ανδρέας</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>antoniafrangou2026</t>
+          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1668,13 +1668,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>4999</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
@@ -1686,33 +1686,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Φλουρεντζου Μάριος</t>
+          <t>Χατζηπαυλου Αυγή</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marios Flourentzou</t>
+          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
       <c r="G21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5999</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1724,24 +1724,24 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Φλουρέντζου Μάριος</t>
+          <t>Χατζηανδρεου Άντρη</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
+          <t>University of Limassol</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -1762,33 +1762,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Φελλας Μιχάλης</t>
+          <t>Χαραλάμπους Χαράλαμπος</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Michalis Fellas</t>
+          <t>Ergodotisi</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>19999</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1800,33 +1800,33 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Τσολάκη Ευανθία</t>
+          <t>Χαραλάμπους Χάρις</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ευανθία - Εύη - Τσολάκη</t>
+          <t>Madame Figaro Cyprus</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F24" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>249999</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -1838,33 +1838,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Τσατσου Θεόδωρος</t>
+          <t>Χαπεσιάν Άρι</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
+          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
         <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>2999</v>
+        <v>14999</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1876,33 +1876,33 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Τσαγγάρης Ανδρέας</t>
+          <t>Χαμπούλλας Ευγένιος</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
@@ -1914,17 +1914,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Σωτηρίου Ανδρέας</t>
+          <t>Φράγκου Αντωνία</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ΔΕΚ - Δημοκρατικό Εθνικό Κίνημα</t>
+          <t>antoniafrangou2026</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1934,13 +1934,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5999</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1952,33 +1952,33 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Στέλιος</t>
+          <t>Φλουρεντζου Μάριος</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ΕΝΕΡΓΟΙ ΠΟΛΙΤΕΣ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Stelios Stylianou</t>
+          <t>Marios Flourentzou</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8999</v>
+        <v>5999</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
@@ -1990,24 +1990,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Φλουρέντζου Μάριος</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>olathrepivatis</t>
+          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2028,33 +2028,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Φελλας Μιχάλης</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Μάριος Στυλιανού</t>
+          <t>Michalis Fellas</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>27</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4999</v>
+        <v>19999</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>0</v>
@@ -2066,33 +2066,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Τσολάκη Ευανθία</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marios Stylianou</t>
+          <t>Ευανθία - Εύη - Τσολάκη</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>249999</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2104,24 +2104,24 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Γιώργος</t>
+          <t>Τσατσου Θεόδωρος</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Δημοκρατική Αλλαγή</t>
+          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>1</v>
@@ -2130,7 +2130,7 @@
         <v>99</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3999</v>
+        <v>2999</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
@@ -2142,24 +2142,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Στυλιανού Γιάννος</t>
+          <t>Τσαγγάρης Ανδρέας</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ΕΔΕΚ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Στυλιανού Γιάννος</t>
+          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
         <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="53" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2301,191 +2301,191 @@
         <v>99</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24999</v>
+        <v>29999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>8811</v>
+        <v>9009</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>620911</v>
+        <v>670909</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Παπαβασιλείου Σταμάτης</t>
+          <t>Κληρίδης Αλέξανδρος</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ΟΙΚΟΛΟΓΟΙ</t>
+          <t>ΔΑ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Σταμάτης Στάμος Παπαβασιλείου</t>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>699</v>
       </c>
       <c r="H5" t="n">
-        <v>19999</v>
+        <v>399999</v>
       </c>
       <c r="I5" t="n">
-        <v>1485</v>
+        <v>898</v>
       </c>
       <c r="J5" t="n">
-        <v>126985</v>
+        <v>479998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης</t>
+          <t>Παπαβασιλείου Σταμάτης</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΟΙΚΟΛΟΓΟΙ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
+          <t>Σταμάτης Στάμος Παπαβασιλείου</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>499</v>
+        <v>99</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>199999</v>
+        <v>19999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>693</v>
+        <v>1485</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>114993</v>
+        <v>126985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ερωτοκρίτου Χριστιάνα</t>
+          <t>Φελλάς Μιχάλης</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Χριστιάνα Ερωτοκρίτου</t>
+          <t>Φελλάς Μιχάλης Δημοτικός Σύμβουλος Λεμεσού</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>199</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>89999</v>
+        <v>199999</v>
       </c>
       <c r="I7" t="n">
-        <v>792</v>
+        <v>693</v>
       </c>
       <c r="J7" t="n">
-        <v>90992</v>
+        <v>114993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>Ερωτοκρίτου Χριστιάνα</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ - AKEL</t>
+          <t>Χριστιάνα Ερωτοκρίτου</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>24999</v>
+        <v>89999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>594</v>
+        <v>792</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49994</v>
+        <v>90992</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Πετρίδης Χαράλαμπος</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
+          <t>ΑΚΕΛ - AKEL</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>99</v>
@@ -2494,112 +2494,112 @@
         <v>24999</v>
       </c>
       <c r="I9" t="n">
-        <v>297</v>
+        <v>594</v>
       </c>
       <c r="J9" t="n">
-        <v>35997</v>
+        <v>49994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Σαββίδης Χρύσανθος</t>
+          <t>Πετρίδης Χαράλαμπος</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Χρύσανθος Σαββίδης</t>
+          <t>Χαράλαμπος Πετρίδης - Charalambos Petrides</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>149999</v>
+        <v>24999</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33998</v>
+        <v>35997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Νικολαΐδης Ζήνωνας</t>
+          <t>Σαββίδης Χρύσανθος</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ΟΙΚΟΛΟΓΟΙ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zenonas Nicolaides</t>
+          <t>Χρύσανθος Σαββίδης</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="H11" t="n">
-        <v>14999</v>
+        <v>149999</v>
       </c>
       <c r="I11" t="n">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="J11" t="n">
-        <v>14999</v>
+        <v>33998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Μούντουκκος Κωνσταντίνος</t>
+          <t>Νικολαΐδης Ζήνωνας</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΟΙΚΟΛΟΓΟΙ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Constantinos Mountouckos</t>
+          <t>Zenonas Nicolaides</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>99</v>
@@ -2617,207 +2617,207 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Θεμιστοκλέους Ανδρέας</t>
+          <t>Μούντουκκος Κωνσταντίνος</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
+          <t>Constantinos Mountouckos</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>5999</v>
+        <v>14999</v>
       </c>
       <c r="I13" t="n">
-        <v>297</v>
+        <v>99</v>
       </c>
       <c r="J13" t="n">
-        <v>8997</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Σενέκης Χρίστος</t>
+          <t>Παλιος Νίκος</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Χρίστος Σενέκης</t>
+          <t>Νίκος Παλιός</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>3999</v>
+        <v>14999</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3999</v>
+        <v>11998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Τσιρίδου Φωτεινή</t>
+          <t>Παπαδοπουλος Γεώργιος</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
+          <t>Γεώργιος Παπαδόπουλος-Georgios Papadopoulos</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
         <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>99</v>
       </c>
       <c r="H15" t="n">
-        <v>39999</v>
+        <v>8999</v>
       </c>
       <c r="I15" t="n">
         <v>99</v>
       </c>
       <c r="J15" t="n">
-        <v>999</v>
+        <v>8999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Χειμωνίδης Ανδρέας</t>
+          <t>Θεμιστοκλέους Ανδρέας</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΔΕΚ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
+          <t>Ανδρέας Χρ. Θεμιστοκλέους</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4999</v>
+        <v>5999</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Χατζηπαυλου Αυγή</t>
+          <t>Σενέκης Χρίστος</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
+          <t>Χρίστος Σενέκης</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3999</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Χαπεσιάν Άρι</t>
+          <t>Τσιρίδου Φωτεινή</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
+          <t>Φωτεινή Τσιρίδου - Fotini Tsiridou</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -2827,51 +2827,51 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>14999</v>
+        <v>39999</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Χρίστου Έλεν</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>Tothemaonline.com</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2883,17 +2883,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Φράγκου Αντωνία</t>
+          <t>Χειμωνίδης Ανδρέας</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>antoniafrangou2026</t>
+          <t>Δρ Ανδρέας Χειμωνίδης - Υποψήφιος Βουλευτής Λεμεσού</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -2903,13 +2903,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>4999</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
@@ -2921,33 +2921,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Φλουρεντζου Μάριος</t>
+          <t>Χατζηπαυλου Αυγή</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marios Flourentzou</t>
+          <t>ΠΟΓΟ Λευκωσίας - Κερύνειας</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
       <c r="G21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5999</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2959,24 +2959,24 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Φλουρέντζου Μάριος</t>
+          <t>Χατζηανδρεου Άντρη</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
+          <t>University of Limassol</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -2997,33 +2997,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Φελλας Μιχάλης</t>
+          <t>Χαραλάμπους Χαράλαμπος</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Michalis Fellas</t>
+          <t>Ergodotisi</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>19999</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3035,33 +3035,33 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Τσολάκη Ευανθία</t>
+          <t>Χαραλάμπους Χάρις</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ευανθία - Εύη - Τσολάκη</t>
+          <t>Madame Figaro Cyprus</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F24" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>249999</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -3073,33 +3073,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Τσατσου Θεόδωρος</t>
+          <t>Χαπεσιάν Άρι</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
+          <t>Ari Habeshian-Άρι Χαπεσιάν</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
         <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>2999</v>
+        <v>14999</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3111,33 +3111,33 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Τσαγγάρης Ανδρέας</t>
+          <t>Χαμπούλλας Ευγένιος</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
@@ -3149,17 +3149,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Σωτηρίου Ανδρέας</t>
+          <t>Φράγκου Αντωνία</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ΔΕΚ - Δημοκρατικό Εθνικό Κίνημα</t>
+          <t>antoniafrangou2026</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5999</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3187,33 +3187,33 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Στέλιος</t>
+          <t>Φλουρεντζου Μάριος</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ΕΝΕΡΓΟΙ ΠΟΛΙΤΕΣ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Stelios Stylianou</t>
+          <t>Marios Flourentzou</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8999</v>
+        <v>5999</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
@@ -3225,24 +3225,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Φλουρέντζου Μάριος</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>olathrepivatis</t>
+          <t>Μάριος Φλουρέντζου - Μαζί για την Αμμόχωστο</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -3263,33 +3263,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Φελλας Μιχάλης</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Μάριος Στυλιανού</t>
+          <t>Michalis Fellas</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>27</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>99</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4999</v>
+        <v>19999</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>0</v>
@@ -3301,33 +3301,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Στυλιανού Μάριος</t>
+          <t>Τσολάκη Ευανθία</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ΑΚΕΛ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marios Stylianou</t>
+          <t>Ευανθία - Εύη - Τσολάκη</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>249999</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3339,24 +3339,24 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανού Γιώργος</t>
+          <t>Τσατσου Θεόδωρος</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ΔΕΚ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Δημοκρατική Αλλαγή</t>
+          <t>Θεόδωρος Τσάτσου - Theodoros Tsatsou</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>1</v>
@@ -3365,7 +3365,7 @@
         <v>99</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3999</v>
+        <v>2999</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
@@ -3377,24 +3377,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Στυλιανού Γιάννος</t>
+          <t>Τσαγγάρης Ανδρέας</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ΕΔΕΚ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Στυλιανού Γιάννος</t>
+          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
         <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3423,18 +3423,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3503,27 +3503,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Αποστόλου Ανδρέας</t>
+          <t>Χαραλάμπους Χαράλαμπος</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Λάρνακα</t>
+          <t>Λευκωσία</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ανδρέας Αποστόλου</t>
+          <t>Ergodotisi</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1487057523117672</t>
+          <t>1476107783797699</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Αποστόλου Ανδρέας</t>
+          <t>Γεωργίου Ανδρέας</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Λάρνακα</t>
+          <t>Λευκωσία</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ανδρέας Αποστόλου</t>
+          <t>Alpha.Jobs</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1306697298055790</t>
+          <t>1297735018495867</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -3581,27 +3581,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Αποστόλου Ανδρέας</t>
+          <t>Μαρία Λοΐζου</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Λάρνακα</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ανδρέας Αποστόλου</t>
+          <t>Alphamega Hypermarkets</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>983246817526090</t>
+          <t>2149168159204570</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -3620,27 +3620,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Βραχιμη Έλενα</t>
+          <t>Μαρία Λοΐζου</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ΔΗΠΑ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>elena.vrachimi</t>
+          <t>Alphamega Hypermarkets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3098730580322147</t>
+          <t>26991771133789928</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -3659,27 +3659,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Παύλου Τίνα</t>
+          <t>Μαρία Λοΐζου</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Τίνα Παύλου - Tina Pavlou</t>
+          <t>Alphamega Hypermarkets</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1562101292295739</t>
+          <t>986611744091926</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -3698,27 +3698,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Παύλου Τίνα</t>
+          <t>Μαρία Λοΐζου</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Τίνα Παύλου - Tina Pavlou</t>
+          <t>Alphamega Hypermarkets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>990122986696911</t>
+          <t>921117457550165</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -3737,7 +3737,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Παλιος Νίκος</t>
+          <t>Μαρία Λοΐζου</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3747,17 +3747,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Πάφος</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Νίκος Παλιός</t>
+          <t>Alphamega Hypermarkets</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2183084272232004</t>
+          <t>979096981638351</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -3776,27 +3776,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Παλιος Νίκος</t>
+          <t>Μηνά Δημήτρης</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ΑΜΔΗ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Πάφος</t>
+          <t>Κερύνεια</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Νίκος Παλιός</t>
+          <t>NovelTime - Romance &amp; Stories</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1663421498115550</t>
+          <t>1917135515651129</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -3815,27 +3815,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Μηνά Δημήτρης</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Λεμεσός</t>
+          <t>Κερύνεια</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>NovelTime - Romance &amp; Stories</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1533738934832768</t>
+          <t>1332557832090200</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3854,27 +3854,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Λαούρης Γιάννης</t>
+          <t>Μηνά Δημήτρης</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ΑΜΔΗ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Κερύνεια</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yiannis Laouris</t>
+          <t>NovelTime - Romance &amp; Stories</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3658020847678930</t>
+          <t>1717259829429326</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -3893,27 +3893,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Κωμοδρομος Χρίστος</t>
+          <t>Μηνά Δημήτρης</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ΑΛΜΑ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Πάφος</t>
+          <t>Κερύνεια</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Κωμοδρόμος Χρίστος</t>
+          <t>NovelTime - Romance &amp; Stories</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1477086877186557</t>
+          <t>2483571052113766</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3932,27 +3932,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Παπαδημητρης Δημήτρης</t>
+          <t>Χαραλάμπους Χάρις</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Πάφος</t>
+          <t>Λευκωσία</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dimitris Papadimitris</t>
+          <t>Madame Figaro Cyprus</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>964206096534079</t>
+          <t>1698296084685137</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -3971,12 +3971,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Στυλιανου Αντώνης</t>
+          <t>Σταύρου Σταύρος</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Antonis Stylianou</t>
+          <t>Salonica View</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2236900650441469</t>
+          <t>848597957706495</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -4010,27 +4010,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Γεωργιάδης Δήμος</t>
+          <t>Σταύρου Σταύρος</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΔΗΠΑ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Κερύνεια</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Δήμος Γεωργιάδης</t>
+          <t>Salonica View</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24770095852687898</t>
+          <t>1137639881860545</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Αθανασιάδης Ζαχαρίας</t>
+          <t>Πουλλικκάς Μάριος</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -4059,17 +4059,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Λεμεσός</t>
+          <t>Λευκωσία</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ζαχαρίας Αθανασιάδης</t>
+          <t>Φωνὴ Ἐλευθερίας</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1468385171652959</t>
+          <t>907918235601834</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4088,12 +4088,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Λαούρης Γιάννης</t>
+          <t>Δρουσιώτης Μακάριος</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ΑΜΔΗ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yiannis Laouris</t>
+          <t>Politis.com.cy - Εφημερίδα Πολίτης</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26858113073822656</t>
+          <t>1322737819819792</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -4127,12 +4127,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Παύλου Τίνα</t>
+          <t>Στεφανου Στέφανος</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Τίνα Παύλου - Tina Pavlou</t>
+          <t>StefansXXL</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4470215903222619</t>
+          <t>928294396848595</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4166,27 +4166,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Στεφανου Στέφανος</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Λεμεσός</t>
+          <t>Λευκωσία</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>StefansXXL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>982291754490345</t>
+          <t>1276652384663474</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -4205,27 +4205,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Μανώλη Θεολόγου Άνδρεα</t>
+          <t>Ανδρέου Γιώργος</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΣΥ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Λάρνακα</t>
+          <t>Αμμόχωστος</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>andrea.th.manoli</t>
+          <t>Eparxiaki</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1494821442309510</t>
+          <t>3140507902799311</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -4244,27 +4244,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Χαμπούλλας Ευγένιος</t>
+          <t>Ανδρέου Γιώργος</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ΕΛΑΜ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Λεμεσός</t>
+          <t>Αμμόχωστος</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+          <t>Eparxiaki</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3040860612787824</t>
+          <t>1309682218005851</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -4283,27 +4283,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Παπαδοπουλος Γεώργιος</t>
+          <t>Νεοφύτου Μάριος</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ΔΗΚΟ</t>
+          <t>ΑΛΜΑ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Λεμεσός</t>
+          <t>Πάφος</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Γεώργιος Παπαδόπουλος-Georgios Papadopoulos</t>
+          <t>Football Manifesto</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25881752421497748</t>
+          <t>1688304108989898</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -4322,27 +4322,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Τσαγγάρης Ανδρέας</t>
+          <t>Γεωργίου Γιώργος</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>ΔΗΣΥ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Πάφος</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
+          <t>University of Nicosia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>965092452908208</t>
+          <t>2262337831238359</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -4361,12 +4361,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Νικολάου Μαρίνα</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΑΚΕΛ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>SuperSport 104</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2690009484700635</t>
+          <t>993604093350523</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -4400,27 +4400,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Κορύτσα Μαρία</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΕΛΑΜ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Αμμόχωστος</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Μαρία Κορυτσά</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1269104821784434</t>
+          <t>813726091505369</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -4439,12 +4439,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Χαραλάμπους Χαράλαμπος</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Ergodotisi</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1229232892187047</t>
+          <t>1505587851002766</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -4478,12 +4478,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Χαραλάμπους Χαράλαμπος</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΕΔΕΚ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Ergodotisi</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1245352974236360</t>
+          <t>1451050616327798</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -4517,12 +4517,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Γεωργίου Ανδρέας</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Alpha.Jobs</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2032794150599870</t>
+          <t>734274829776726</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -4556,12 +4556,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Γεωργίου Ανδρέας</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΔΗΚΟ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Alpha.Jobs</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1235859935360736</t>
+          <t>1309311293991559</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -4595,27 +4595,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Κληρίδης Αλέξανδρος</t>
+          <t>Μαρία Λοΐζου</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ΔΑ</t>
+          <t>ΑΜΔΗ</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Λευκωσία</t>
+          <t>Λεμεσός</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+          <t>Alphamega Hypermarkets</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1468353658340842</t>
+          <t>960163230162805</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -4625,11 +4625,2602 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Μηνά Δημήτρης</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NovelTime - Romance &amp; Stories</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>915802601489645</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Μηνά Δημήτρης</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NovelTime - Romance &amp; Stories</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1509162714119011</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Μηνά Δημήτρης</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NovelTime - Romance &amp; Stories</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>947018148138762</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Μηνά Δημήτρης</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>NovelTime - Romance &amp; Stories</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1259468489275660</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Μηνά Δημήτρης</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NovelTime - Romance &amp; Stories</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4252255755035302</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Κυπριανου Κύπρος</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Stavrinos-estates Cyprus Πωλήσεις οικιών ,διαμερισμάτων, οικοπέδων Λευκωσία</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2238480093558959</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Κυπριανου Κύπρος</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Stavrinos-estates Cyprus Πωλήσεις οικιών ,διαμερισμάτων, οικοπέδων Λευκωσία</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2193159177888343</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Μάριος Σταύρου</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Cyprus</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1451889266260598</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Μάριος Σταύρου</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lidl Cyprus</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1435696728358991</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Χρίστου Έλεν</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Tothemaonline.com</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1976131796326847</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Σταύρου Σταύρος</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Salonica View</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>968657992756696</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Αντωνίου Μάριος</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>IMH</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1689667272382547</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Δρουσιώτης Μακάριος</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Politis.com.cy - Εφημερίδα Πολίτης</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>961216910136841</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Δρουσιώτης Μακάριος</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Politis.com.cy - Εφημερίδα Πολίτης</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1013525551207954</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Στεφανου Στέφανος</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>StefansXXL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>950630600925493</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Στεφανου Στέφανος</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>StefansXXL</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1669730104262023</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Στεφανου Στέφανος</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>StefansXXL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1627047001745151</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Χατζηανδρεου Άντρη</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>University of Limassol</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1508201797348498</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Χατζηανδρεου Άντρη</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>University of Limassol</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1463273671778307</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Χατζηανδρεου Άντρη</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>University of Limassol</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1482743600313958</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Χατζηανδρεου Άντρη</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>University of Limassol</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>949382834673049</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Χατζηανδρεου Άντρη</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>University of Limassol</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1649377436312027</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Χατζηανδρεου Άντρη</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ΑΚΕΛ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>University of Limassol</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2144626713001056</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Γεωργιάδης Δήμος</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Γεωργιάδης</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1303700075068172</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Μιχαήλ Ελένη</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ΔΕΚ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>M &amp; A Creation</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2384720728723715</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Μιχαήλ Ελένη</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ΔΕΚ</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>M &amp; A Creation</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1015522771137118</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Νικολάου Αντρέας</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ΔΗΚΟ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Agia Napa Municipality - Δήμος Αγίας Νάπας</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>981971367647808</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Νικολάου Αντρέας</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΚΟ</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Agia Napa Municipality - Δήμος Αγίας Νάπας</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>867528248932938</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Θεοφάνους Γιώργος</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ΒΟΛΤ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>partylinecyprus</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>942738208586165</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Στυλιανού Μάριος</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ΑΛΜΑ</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Μάριος Στυλιανού</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1696038684870609</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Αθανασιάδης Ζαχαρίας</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ΕΛΑΜ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ζαχαρίας Αθανασιάδης</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1330888802244834</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Σταύρου Σταύρος</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Partyline Cyprus</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>954479320538604</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Μιχαηλίδης Γιώργος</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Εθνικό Κέντρο Συντονισμού Κυβερνοασφάλειας Κύπρου - ΝCCcy</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1013981367632056</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Παύλου Τίνα</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Τίνα Παύλου - Tina Pavlou</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>35380689674908199</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Μενελαου Ελένη</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Αμμόχωστος</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Eλένη Μενελάου/Eleni Menelaou</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>955755290411400</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Ελληνας Σάββας</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Έλληνας Σάββας</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>4446806865575192</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Αποστόλου Ανδρέας</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ΔΗΚΟ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ανδρέας Αποστόλου</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1487057523117672</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>15,000–19,999</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0–99</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Αποστόλου Ανδρέας</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΚΟ</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Ανδρέας Αποστόλου</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1306697298055790</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Αποστόλου Ανδρέας</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ΔΗΚΟ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ανδρέας Αποστόλου</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>983246817526090</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>25,000–29,999</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0–99</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Βραχιμη Έλενα</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΠΑ</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>elena.vrachimi</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>3098730580322147</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Παύλου Τίνα</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Τίνα Παύλου - Tina Pavlou</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1562101292295739</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Παύλου Τίνα</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Τίνα Παύλου - Tina Pavlou</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>990122986696911</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Παλιος Νίκος</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Νίκος Παλιός</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2183084272232004</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3,000–3,999</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0–99</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Παλιος Νίκος</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Νίκος Παλιός</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1663421498115550</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>7,000–7,999</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>0–99</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Χαμπούλλας Ευγένιος</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ΕΛΑΜ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1533738934832768</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Λαούρης Γιάννης</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Yiannis Laouris</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3658020847678930</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Κωμοδρομος Χρίστος</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ΑΛΜΑ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Κωμοδρόμος Χρίστος</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1477086877186557</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Παπαδημητρης Δημήτρης</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ΕΛΑΜ</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Πάφος</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Dimitris Papadimitris</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>964206096534079</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Στυλιανου Αντώνης</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Antonis Stylianou</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2236900650441469</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Γεωργιάδης Δήμος</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Κερύνεια</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Γεωργιάδης</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>24770095852687898</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Αθανασιάδης Ζαχαρίας</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ΕΛΑΜ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ζαχαρίας Αθανασιάδης</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1468385171652959</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Λαούρης Γιάννης</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ΑΜΔΗ</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Yiannis Laouris</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>26858113073822656</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Παύλου Τίνα</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Τίνα Παύλου - Tina Pavlou</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>4470215903222619</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Χαμπούλλας Ευγένιος</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ΕΛΑΜ</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>982291754490345</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Μανώλη Θεολόγου Άνδρεα</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ΔΗΣΥ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Λάρνακα</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>andrea.th.manoli</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1494821442309510</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Χαμπούλλας Ευγένιος</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>ΕΛΑΜ</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Evgenios Hamboullas | Ευγένιος Χαμπουλλάς</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3040860612787824</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Παπαδοπουλος Γεώργιος</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ΔΗΚΟ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Γεώργιος Παπαδόπουλος-Georgios Papadopoulos</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>25881752421497748</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>8,000–8,999</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0–99</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Τσαγγάρης Ανδρέας</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ΣΗΚΟΥ ΠΑΝΩ</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Αντρέας Τσαγγάρης - ΣΗΚΟΥ ΠΑΝΩ</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>965092452908208</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2690009484700635</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>350,000–399,999</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>600–699</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1269104821784434</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1229232892187047</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1245352974236360</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2032794150599870</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1235859935360736</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>70,000–79,999</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>100–199</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Κληρίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ΔΑ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Λευκωσία</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Αλέξανδρος Κληρίδης / Alexandros Clerides</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1468353658340842</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4662,6 +7253,71 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
